--- a/py/figure/test2/test2_error.xlsx
+++ b/py/figure/test2/test2_error.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2023_IPIN_Competition_Track03\py\figure\test2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D623CF4D-7C23-4470-84DF-A08DC7F4996A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55486F03-42B7-4274-8907-DE9429171254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8220" yWindow="1428" windowWidth="23040" windowHeight="12204" xr2:uid="{27DAA2EC-07AC-43C6-81D7-23A2318EAE70}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{27DAA2EC-07AC-43C6-81D7-23A2318EAE70}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -454,7 +454,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{235A2938-6F30-4E28-9976-966FD799CEE3}">
-  <dimension ref="A1:B14"/>
+  <dimension ref="A1:D14"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.33203125" style="1" customWidth="1"/>
@@ -462,39 +462,51 @@
     <col min="3" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1">
         <v>7.47</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D1" s="1">
+        <v>6.65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="1">
         <v>5.58</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D2" s="1">
+        <v>4.7300000000000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="1">
         <v>4.97</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D3" s="1">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="1">
         <v>33.97</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D4" s="1">
+        <v>14.41</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>4</v>
       </c>
@@ -502,7 +514,7 @@
         <v>8.15</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
@@ -510,7 +522,7 @@
         <v>6.95</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
@@ -518,7 +530,7 @@
         <v>4.2699999999999996</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>7</v>
       </c>
@@ -526,36 +538,48 @@
         <v>26.58</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B11" s="1">
         <v>7.17</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D11" s="1">
+        <v>6.54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B12" s="1">
         <v>5.77</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D12" s="1">
+        <v>5.29</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
       <c r="B13" s="1">
         <v>4.25</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="D13" s="1">
+        <v>3.85</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B14" s="1">
         <v>27.05</v>
+      </c>
+      <c r="D14" s="1">
+        <v>12.97</v>
       </c>
     </row>
   </sheetData>

--- a/py/figure/test2/test2_error.xlsx
+++ b/py/figure/test2/test2_error.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2023_IPIN_Competition_Track03\py\figure\test2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55486F03-42B7-4274-8907-DE9429171254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DAE5685-6BA2-49F1-8860-172D1AFA5946}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" xr2:uid="{27DAA2EC-07AC-43C6-81D7-23A2318EAE70}"/>
+    <workbookView xWindow="13584" yWindow="1872" windowWidth="23040" windowHeight="12204" xr2:uid="{27DAA2EC-07AC-43C6-81D7-23A2318EAE70}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -513,6 +513,9 @@
       <c r="B6" s="1">
         <v>8.15</v>
       </c>
+      <c r="D6" s="1">
+        <v>8.58</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
@@ -521,6 +524,9 @@
       <c r="B7" s="1">
         <v>6.95</v>
       </c>
+      <c r="D7" s="1">
+        <v>7.42</v>
+      </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
@@ -529,6 +535,9 @@
       <c r="B8" s="1">
         <v>4.2699999999999996</v>
       </c>
+      <c r="D8" s="1">
+        <v>4.3099999999999996</v>
+      </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
@@ -536,6 +545,9 @@
       </c>
       <c r="B9" s="1">
         <v>26.58</v>
+      </c>
+      <c r="D9" s="1">
+        <v>21.02</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.3">
